--- a/Test/Assets/Excel/ExcelData.xlsx
+++ b/Test/Assets/Excel/ExcelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\卒制\Graduation-Project\Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD26123-88D0-4FF0-BEA8-88912BA097F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DDDC4E-4C0B-439D-BEA7-A328AC726158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2BA82EEB-B8B9-4BF1-A7F3-81E7AF626BF5}"/>
   </bookViews>
@@ -1072,7 +1072,7 @@
         <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
         <v>25</v>

--- a/Test/Assets/Excel/ExcelData.xlsx
+++ b/Test/Assets/Excel/ExcelData.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\卒制\Graduation-Project\Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DDDC4E-4C0B-439D-BEA7-A328AC726158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB31652-F848-44F8-879C-9AEB80B5566E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2BA82EEB-B8B9-4BF1-A7F3-81E7AF626BF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemy" sheetId="1" r:id="rId1"/>
+    <sheet name="MoveBoss" sheetId="2" r:id="rId2"/>
+    <sheet name="DepthBoss" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="61">
   <si>
     <t>id</t>
     <phoneticPr fontId="1"/>
@@ -241,6 +243,30 @@
   </si>
   <si>
     <t>ShieldEnemy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bulletRate1_2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bulletRate3_4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rotate90PerSec</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>changeHPPercent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>maxLoop</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>maxLRTackle</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -248,7 +274,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,6 +293,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -295,11 +328,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -637,7 +673,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D28F37CA-1AF4-42DB-90C7-EECEDCB7D491}">
   <dimension ref="A1:W15"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="11.8984375" customWidth="1"/>
     <col min="4" max="4" width="10.69921875" customWidth="1"/>
@@ -652,7 +688,7 @@
     <col min="23" max="23" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -723,7 +759,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -738,9 +774,9 @@
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:23">
       <c r="A3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>28</v>
@@ -809,7 +845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>101</v>
       </c>
@@ -847,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>102</v>
       </c>
@@ -897,7 +933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>103</v>
       </c>
@@ -947,7 +983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>201</v>
       </c>
@@ -976,7 +1012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>202</v>
       </c>
@@ -1017,7 +1053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>203</v>
       </c>
@@ -1058,7 +1094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>301</v>
       </c>
@@ -1087,7 +1123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>401</v>
       </c>
@@ -1131,7 +1167,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>501</v>
       </c>
@@ -1160,7 +1196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1225,7 +1261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:23">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1257,7 +1293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:23">
       <c r="A15">
         <v>3</v>
       </c>
@@ -1307,4 +1343,78 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5202F1E3-3E72-46DC-8172-F7E61DBED269}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="2" width="15.19921875" customWidth="1"/>
+    <col min="3" max="3" width="13.3984375" customWidth="1"/>
+    <col min="4" max="4" width="15.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7028EC9-363A-4E20-B1ED-A996FB4B3D45}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="11.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Test/Assets/Excel/ExcelData.xlsx
+++ b/Test/Assets/Excel/ExcelData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\卒制\Graduation-Project\Test\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\show-\OneDrive\デスクトップ\卒業制作\Graduation-Project\Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB31652-F848-44F8-879C-9AEB80B5566E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920608B9-A684-4A1A-83A1-914DB1BFCA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2BA82EEB-B8B9-4BF1-A7F3-81E7AF626BF5}"/>
+    <workbookView xWindow="4824" yWindow="4008" windowWidth="17280" windowHeight="8964" xr2:uid="{2BA82EEB-B8B9-4BF1-A7F3-81E7AF626BF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemy" sheetId="1" r:id="rId1"/>
@@ -1269,7 +1269,7 @@
         <v>43</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D14" t="s">
         <v>39</v>
